--- a/data/gravel/No22 Drifter X 2025.xlsx
+++ b/data/gravel/No22 Drifter X 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B4C1D3-6E4C-E141-9595-261BA106D383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F701C6-2BBC-8740-BA95-7B8940BBBE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35360" yWindow="-16980" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8060" yWindow="1140" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -326,9 +326,6 @@
     <t>Stack (mm)</t>
   </si>
   <si>
-    <t>https://22bicycles.com/products/drifter-adventure?variant=44539401601197</t>
-  </si>
-  <si>
     <t>No.22</t>
   </si>
   <si>
@@ -339,6 +336,12 @@
   </si>
   <si>
     <t>No. 6 gravel fork</t>
+  </si>
+  <si>
+    <t>https://22bicycles.com/products/drifter-x?variant=44539391672493</t>
+  </si>
+  <si>
+    <t>https://22bicycles.com/cdn/shop/files/DrifterXProfile.jpg?v=1748999930</t>
   </si>
 </sst>
 </file>
@@ -712,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -720,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -744,7 +747,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1098,7 +1106,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="1">
         <v>752</v>
@@ -1164,7 +1172,7 @@
         <v>382</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">

--- a/data/gravel/No22 Drifter X 2025.xlsx
+++ b/data/gravel/No22 Drifter X 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F701C6-2BBC-8740-BA95-7B8940BBBE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C902BF51-A1FA-3E40-BD5E-9973B33E3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8060" yWindow="1140" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -266,9 +266,6 @@
     <t>a8:i32</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>threaded</t>
   </si>
   <si>
@@ -342,6 +339,15 @@
   </si>
   <si>
     <t>https://22bicycles.com/cdn/shop/files/DrifterXProfile.jpg?v=1748999930</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Johnstown, New York, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -704,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -715,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -723,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -747,12 +753,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -776,28 +782,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -806,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="1">
         <v>502</v>
@@ -836,7 +842,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1">
         <v>440</v>
@@ -866,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1">
         <v>110</v>
@@ -896,7 +902,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="1">
         <v>75</v>
@@ -926,7 +932,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" s="1">
         <v>70.2</v>
@@ -956,7 +962,7 @@
         <v>75</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="1">
         <v>579</v>
@@ -986,7 +992,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" s="1">
         <v>423</v>
@@ -1016,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="1">
         <v>75</v>
@@ -1046,7 +1052,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="1">
         <v>359</v>
@@ -1076,7 +1082,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" s="1">
         <v>523</v>
@@ -1106,7 +1112,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C19" s="1">
         <v>752</v>
@@ -1172,7 +1178,7 @@
         <v>382</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -1636,7 +1642,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -1968,7 +1974,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -1979,6 +1985,14 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/No22 Drifter X 2025.xlsx
+++ b/data/gravel/No22 Drifter X 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C902BF51-A1FA-3E40-BD5E-9973B33E3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E491D66B-2BA6-C24C-90E7-7744273DFFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -710,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1639,11 +1657,9 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -1655,7 +1671,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1669,11 +1685,9 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="1">
-        <v>27.2</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1685,7 +1699,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1699,7 +1713,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1713,7 +1727,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1727,9 +1741,11 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -1741,7 +1757,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1755,9 +1771,11 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B57" s="1">
+        <v>27.2</v>
+      </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -1769,7 +1787,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1783,7 +1801,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -1797,7 +1815,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -1811,7 +1829,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -1825,7 +1843,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -1839,7 +1857,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -1853,7 +1871,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -1867,7 +1885,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1881,7 +1899,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1895,7 +1913,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1909,7 +1927,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -1923,11 +1941,9 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B69" s="1">
-        <v>6499</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -1939,11 +1955,9 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B70" s="1">
-        <v>12111</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -1955,11 +1969,9 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -1971,11 +1983,9 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -1986,10 +1996,102 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="1">
+        <v>6499</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="1">
+        <v>12111</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>102</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>103</v>
       </c>
     </row>

--- a/data/gravel/No22 Drifter X 2025.xlsx
+++ b/data/gravel/No22 Drifter X 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E491D66B-2BA6-C24C-90E7-7744273DFFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360A09A7-5DD4-8C42-96FB-880C9950072C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>optional</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1890,9 @@
       <c r="A65" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B65" s="1"/>
+      <c r="B65" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
